--- a/docs/htr/transkrib_corpus_b.xlsx
+++ b/docs/htr/transkrib_corpus_b.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eugenia/Desktop/thesis/magic_tagger/docs/htr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB39D07-7657-6A43-83A2-2679B1A1C568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9194B8AD-7AA1-E647-B3CC-834F082806D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2839,7 +2839,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:W513"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2848,10 +2847,9 @@
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="14" hidden="1" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="10" max="12" width="14" hidden="1" customWidth="1"/>
-    <col min="13" max="14" width="14" customWidth="1"/>
-    <col min="15" max="18" width="14" hidden="1" customWidth="1"/>
-    <col min="19" max="21" width="14" customWidth="1"/>
+    <col min="10" max="18" width="14" hidden="1" customWidth="1"/>
+    <col min="19" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="14" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="14" style="17" customWidth="1"/>
     <col min="23" max="28" width="14" customWidth="1"/>
   </cols>
@@ -2927,7 +2925,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="20" customFormat="1" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" s="20" customFormat="1" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>45</v>
       </c>
@@ -2978,7 +2976,7 @@
       </c>
       <c r="W2" s="25"/>
     </row>
-    <row r="3" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
@@ -3027,7 +3025,7 @@
       </c>
       <c r="W3" s="25"/>
     </row>
-    <row r="4" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>47</v>
       </c>
@@ -3078,7 +3076,7 @@
       </c>
       <c r="W4" s="25"/>
     </row>
-    <row r="5" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
         <v>47</v>
       </c>
@@ -3127,7 +3125,7 @@
       </c>
       <c r="W5" s="25"/>
     </row>
-    <row r="6" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
@@ -3178,7 +3176,7 @@
       </c>
       <c r="W6" s="25"/>
     </row>
-    <row r="7" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>29</v>
       </c>
@@ -3227,7 +3225,7 @@
       </c>
       <c r="W7" s="25"/>
     </row>
-    <row r="8" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>29</v>
       </c>
@@ -3276,7 +3274,7 @@
       </c>
       <c r="W8" s="25"/>
     </row>
-    <row r="9" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>29</v>
       </c>
@@ -3325,7 +3323,7 @@
       </c>
       <c r="W9" s="25"/>
     </row>
-    <row r="10" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>29</v>
       </c>
@@ -3374,7 +3372,7 @@
       </c>
       <c r="W10" s="25"/>
     </row>
-    <row r="11" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>29</v>
       </c>
@@ -3423,7 +3421,7 @@
       </c>
       <c r="W11" s="25"/>
     </row>
-    <row r="12" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
@@ -3474,7 +3472,7 @@
       </c>
       <c r="W12" s="25"/>
     </row>
-    <row r="13" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>29</v>
       </c>
@@ -3523,7 +3521,7 @@
       </c>
       <c r="W13" s="25"/>
     </row>
-    <row r="14" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -3572,7 +3570,7 @@
       </c>
       <c r="W14" s="25"/>
     </row>
-    <row r="15" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>29</v>
       </c>
@@ -3621,7 +3619,7 @@
       </c>
       <c r="W15" s="25"/>
     </row>
-    <row r="16" spans="1:23" ht="38" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>29</v>
       </c>
@@ -3670,7 +3668,7 @@
       </c>
       <c r="W16" s="25"/>
     </row>
-    <row r="17" spans="1:23" ht="41" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>29</v>
       </c>
@@ -3719,7 +3717,7 @@
       </c>
       <c r="W17" s="25"/>
     </row>
-    <row r="18" spans="1:23" ht="43" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>29</v>
       </c>
@@ -3784,7 +3782,7 @@
       </c>
       <c r="W18" s="25"/>
     </row>
-    <row r="19" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>29</v>
       </c>
@@ -3839,7 +3837,7 @@
       </c>
       <c r="W19" s="25"/>
     </row>
-    <row r="20" spans="1:23" ht="46" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>29</v>
       </c>
@@ -3888,7 +3886,7 @@
       </c>
       <c r="W20" s="25"/>
     </row>
-    <row r="21" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>29</v>
       </c>
@@ -3937,7 +3935,7 @@
       </c>
       <c r="W21" s="25"/>
     </row>
-    <row r="22" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>29</v>
       </c>
@@ -3986,7 +3984,7 @@
       </c>
       <c r="W22" s="25"/>
     </row>
-    <row r="23" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>29</v>
       </c>
@@ -4035,7 +4033,7 @@
       </c>
       <c r="W23" s="25"/>
     </row>
-    <row r="24" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>29</v>
       </c>
@@ -4084,7 +4082,7 @@
       </c>
       <c r="W24" s="25"/>
     </row>
-    <row r="25" spans="1:23" ht="44" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>29</v>
       </c>
@@ -4133,7 +4131,7 @@
       </c>
       <c r="W25" s="25"/>
     </row>
-    <row r="26" spans="1:23" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>29</v>
       </c>
@@ -4182,7 +4180,7 @@
       </c>
       <c r="W26" s="25"/>
     </row>
-    <row r="27" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>29</v>
       </c>
@@ -4231,7 +4229,7 @@
       </c>
       <c r="W27" s="25"/>
     </row>
-    <row r="28" spans="1:23" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>29</v>
       </c>
@@ -4280,7 +4278,7 @@
       </c>
       <c r="W28" s="25"/>
     </row>
-    <row r="29" spans="1:23" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>29</v>
       </c>
@@ -4329,7 +4327,7 @@
       </c>
       <c r="W29" s="25"/>
     </row>
-    <row r="30" spans="1:23" ht="43" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
@@ -4378,7 +4376,7 @@
       </c>
       <c r="W30" s="25"/>
     </row>
-    <row r="31" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>29</v>
       </c>
@@ -4427,7 +4425,7 @@
       </c>
       <c r="W31" s="25"/>
     </row>
-    <row r="32" spans="1:23" ht="87" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="87" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>29</v>
       </c>
@@ -4476,7 +4474,7 @@
       </c>
       <c r="W32" s="25"/>
     </row>
-    <row r="33" spans="1:23" ht="44" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>29</v>
       </c>
@@ -4525,7 +4523,7 @@
       </c>
       <c r="W33" s="25"/>
     </row>
-    <row r="34" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>29</v>
       </c>
@@ -4574,7 +4572,7 @@
       </c>
       <c r="W34" s="25"/>
     </row>
-    <row r="35" spans="1:23" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>29</v>
       </c>
@@ -4623,7 +4621,7 @@
       </c>
       <c r="W35" s="25"/>
     </row>
-    <row r="36" spans="1:23" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>29</v>
       </c>
@@ -4672,7 +4670,7 @@
       </c>
       <c r="W36" s="25"/>
     </row>
-    <row r="37" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>29</v>
       </c>
@@ -4721,7 +4719,7 @@
       </c>
       <c r="W37" s="25"/>
     </row>
-    <row r="38" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>29</v>
       </c>
@@ -4770,7 +4768,7 @@
       </c>
       <c r="W38" s="25"/>
     </row>
-    <row r="39" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>29</v>
       </c>
@@ -4819,7 +4817,7 @@
       </c>
       <c r="W39" s="25"/>
     </row>
-    <row r="40" spans="1:23" ht="40" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>29</v>
       </c>
@@ -4868,7 +4866,7 @@
       </c>
       <c r="W40" s="25"/>
     </row>
-    <row r="41" spans="1:23" ht="53" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" ht="53" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>30</v>
       </c>
@@ -4921,7 +4919,7 @@
       </c>
       <c r="W41" s="25"/>
     </row>
-    <row r="42" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>30</v>
       </c>
@@ -4974,7 +4972,7 @@
       </c>
       <c r="W42" s="25"/>
     </row>
-    <row r="43" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>30</v>
       </c>
@@ -5025,7 +5023,7 @@
       </c>
       <c r="W43" s="25"/>
     </row>
-    <row r="44" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>30</v>
       </c>
@@ -5076,7 +5074,7 @@
       </c>
       <c r="W44" s="25"/>
     </row>
-    <row r="45" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>30</v>
       </c>
@@ -5127,7 +5125,7 @@
       </c>
       <c r="W45" s="25"/>
     </row>
-    <row r="46" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>30</v>
       </c>
@@ -5178,7 +5176,7 @@
       </c>
       <c r="W46" s="25"/>
     </row>
-    <row r="47" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>30</v>
       </c>
@@ -5229,7 +5227,7 @@
       </c>
       <c r="W47" s="25"/>
     </row>
-    <row r="48" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>30</v>
       </c>
@@ -5280,7 +5278,7 @@
       </c>
       <c r="W48" s="25"/>
     </row>
-    <row r="49" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>30</v>
       </c>
@@ -5331,7 +5329,7 @@
       </c>
       <c r="W49" s="25"/>
     </row>
-    <row r="50" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>30</v>
       </c>
@@ -5382,7 +5380,7 @@
       </c>
       <c r="W50" s="25"/>
     </row>
-    <row r="51" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
         <v>30</v>
       </c>
@@ -5433,7 +5431,7 @@
       </c>
       <c r="W51" s="25"/>
     </row>
-    <row r="52" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>30</v>
       </c>
@@ -5484,7 +5482,7 @@
       </c>
       <c r="W52" s="25"/>
     </row>
-    <row r="53" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
         <v>30</v>
       </c>
@@ -5535,7 +5533,7 @@
       </c>
       <c r="W53" s="25"/>
     </row>
-    <row r="54" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>30</v>
       </c>
@@ -5586,7 +5584,7 @@
       </c>
       <c r="W54" s="25"/>
     </row>
-    <row r="55" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
         <v>30</v>
       </c>
@@ -5637,7 +5635,7 @@
       </c>
       <c r="W55" s="25"/>
     </row>
-    <row r="56" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>30</v>
       </c>
@@ -5688,7 +5686,7 @@
       </c>
       <c r="W56" s="25"/>
     </row>
-    <row r="57" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>30</v>
       </c>
@@ -5739,7 +5737,7 @@
       </c>
       <c r="W57" s="25"/>
     </row>
-    <row r="58" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
         <v>30</v>
       </c>
@@ -5790,7 +5788,7 @@
       </c>
       <c r="W58" s="25"/>
     </row>
-    <row r="59" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>30</v>
       </c>
@@ -5841,7 +5839,7 @@
       </c>
       <c r="W59" s="25"/>
     </row>
-    <row r="60" spans="1:23" ht="34" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
         <v>30</v>
       </c>
@@ -5908,7 +5906,7 @@
       </c>
       <c r="W60" s="25"/>
     </row>
-    <row r="61" spans="1:23" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
         <v>30</v>
       </c>
@@ -5959,7 +5957,7 @@
       </c>
       <c r="W61" s="25"/>
     </row>
-    <row r="62" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
         <v>30</v>
       </c>
@@ -6010,7 +6008,7 @@
       </c>
       <c r="W62" s="25"/>
     </row>
-    <row r="63" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
         <v>30</v>
       </c>
@@ -6061,7 +6059,7 @@
       </c>
       <c r="W63" s="25"/>
     </row>
-    <row r="64" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
         <v>30</v>
       </c>
@@ -6112,7 +6110,7 @@
       </c>
       <c r="W64" s="25"/>
     </row>
-    <row r="65" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
         <v>30</v>
       </c>
@@ -6163,7 +6161,7 @@
       </c>
       <c r="W65" s="25"/>
     </row>
-    <row r="66" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
         <v>30</v>
       </c>
@@ -6214,7 +6212,7 @@
       </c>
       <c r="W66" s="25"/>
     </row>
-    <row r="67" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
         <v>30</v>
       </c>
@@ -6263,7 +6261,7 @@
       </c>
       <c r="W67" s="25"/>
     </row>
-    <row r="68" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
         <v>30</v>
       </c>
@@ -6312,7 +6310,7 @@
       </c>
       <c r="W68" s="25"/>
     </row>
-    <row r="69" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
         <v>30</v>
       </c>
@@ -6363,7 +6361,7 @@
       </c>
       <c r="W69" s="25"/>
     </row>
-    <row r="70" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
         <v>30</v>
       </c>
@@ -6414,7 +6412,7 @@
       </c>
       <c r="W70" s="25"/>
     </row>
-    <row r="71" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
         <v>30</v>
       </c>
@@ -6463,7 +6461,7 @@
       </c>
       <c r="W71" s="25"/>
     </row>
-    <row r="72" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
         <v>30</v>
       </c>
@@ -6512,7 +6510,7 @@
       </c>
       <c r="W72" s="25"/>
     </row>
-    <row r="73" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
         <v>30</v>
       </c>
@@ -6563,7 +6561,7 @@
       </c>
       <c r="W73" s="25"/>
     </row>
-    <row r="74" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
         <v>30</v>
       </c>
@@ -6612,7 +6610,7 @@
       </c>
       <c r="W74" s="25"/>
     </row>
-    <row r="75" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
         <v>30</v>
       </c>
@@ -6663,7 +6661,7 @@
       </c>
       <c r="W75" s="25"/>
     </row>
-    <row r="76" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
         <v>30</v>
       </c>
@@ -6714,7 +6712,7 @@
       </c>
       <c r="W76" s="25"/>
     </row>
-    <row r="77" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
         <v>30</v>
       </c>
@@ -6763,7 +6761,7 @@
       </c>
       <c r="W77" s="25"/>
     </row>
-    <row r="78" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
         <v>30</v>
       </c>
@@ -6812,7 +6810,7 @@
       </c>
       <c r="W78" s="25"/>
     </row>
-    <row r="79" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
         <v>30</v>
       </c>
@@ -6861,7 +6859,7 @@
       </c>
       <c r="W79" s="25"/>
     </row>
-    <row r="80" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A80" s="6" t="s">
         <v>30</v>
       </c>
@@ -6910,7 +6908,7 @@
       </c>
       <c r="W80" s="25"/>
     </row>
-    <row r="81" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
         <v>30</v>
       </c>
@@ -6959,7 +6957,7 @@
       </c>
       <c r="W81" s="25"/>
     </row>
-    <row r="82" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A82" s="6" t="s">
         <v>30</v>
       </c>
@@ -7008,7 +7006,7 @@
       </c>
       <c r="W82" s="25"/>
     </row>
-    <row r="83" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
         <v>30</v>
       </c>
@@ -7057,7 +7055,7 @@
       </c>
       <c r="W83" s="25"/>
     </row>
-    <row r="84" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A84" s="6" t="s">
         <v>30</v>
       </c>
@@ -7106,7 +7104,7 @@
       </c>
       <c r="W84" s="25"/>
     </row>
-    <row r="85" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
         <v>30</v>
       </c>
@@ -7155,7 +7153,7 @@
       </c>
       <c r="W85" s="25"/>
     </row>
-    <row r="86" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
         <v>30</v>
       </c>
@@ -7204,7 +7202,7 @@
       </c>
       <c r="W86" s="25"/>
     </row>
-    <row r="87" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A87" s="6" t="s">
         <v>30</v>
       </c>
@@ -7253,7 +7251,7 @@
       </c>
       <c r="W87" s="25"/>
     </row>
-    <row r="88" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A88" s="6" t="s">
         <v>30</v>
       </c>
@@ -7302,7 +7300,7 @@
       </c>
       <c r="W88" s="25"/>
     </row>
-    <row r="89" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
         <v>30</v>
       </c>
@@ -7351,7 +7349,7 @@
       </c>
       <c r="W89" s="25"/>
     </row>
-    <row r="90" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A90" s="6" t="s">
         <v>30</v>
       </c>
@@ -7400,7 +7398,7 @@
       </c>
       <c r="W90" s="25"/>
     </row>
-    <row r="91" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A91" s="6" t="s">
         <v>30</v>
       </c>
@@ -7449,7 +7447,7 @@
       </c>
       <c r="W91" s="25"/>
     </row>
-    <row r="92" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A92" s="6" t="s">
         <v>30</v>
       </c>
@@ -7498,7 +7496,7 @@
       </c>
       <c r="W92" s="25"/>
     </row>
-    <row r="93" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A93" s="6" t="s">
         <v>30</v>
       </c>
@@ -7547,7 +7545,7 @@
       </c>
       <c r="W93" s="25"/>
     </row>
-    <row r="94" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A94" s="6" t="s">
         <v>30</v>
       </c>
@@ -7596,7 +7594,7 @@
       </c>
       <c r="W94" s="25"/>
     </row>
-    <row r="95" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
         <v>30</v>
       </c>
@@ -7645,7 +7643,7 @@
       </c>
       <c r="W95" s="25"/>
     </row>
-    <row r="96" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A96" s="6" t="s">
         <v>30</v>
       </c>
@@ -7694,7 +7692,7 @@
       </c>
       <c r="W96" s="25"/>
     </row>
-    <row r="97" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A97" s="6" t="s">
         <v>30</v>
       </c>
@@ -7743,7 +7741,7 @@
       </c>
       <c r="W97" s="25"/>
     </row>
-    <row r="98" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A98" s="6" t="s">
         <v>30</v>
       </c>
@@ -7792,7 +7790,7 @@
       </c>
       <c r="W98" s="25"/>
     </row>
-    <row r="99" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A99" s="6" t="s">
         <v>30</v>
       </c>
@@ -7841,7 +7839,7 @@
       </c>
       <c r="W99" s="25"/>
     </row>
-    <row r="100" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A100" s="6" t="s">
         <v>30</v>
       </c>
@@ -7890,7 +7888,7 @@
       </c>
       <c r="W100" s="25"/>
     </row>
-    <row r="101" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A101" s="6" t="s">
         <v>30</v>
       </c>
@@ -7939,7 +7937,7 @@
       </c>
       <c r="W101" s="25"/>
     </row>
-    <row r="102" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A102" s="6" t="s">
         <v>30</v>
       </c>
@@ -7988,7 +7986,7 @@
       </c>
       <c r="W102" s="25"/>
     </row>
-    <row r="103" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A103" s="6" t="s">
         <v>30</v>
       </c>
@@ -8037,7 +8035,7 @@
       </c>
       <c r="W103" s="25"/>
     </row>
-    <row r="104" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A104" s="6" t="s">
         <v>30</v>
       </c>
@@ -8086,7 +8084,7 @@
       </c>
       <c r="W104" s="25"/>
     </row>
-    <row r="105" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A105" s="6" t="s">
         <v>30</v>
       </c>
@@ -8135,7 +8133,7 @@
       </c>
       <c r="W105" s="25"/>
     </row>
-    <row r="106" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A106" s="6" t="s">
         <v>30</v>
       </c>
@@ -8184,7 +8182,7 @@
       </c>
       <c r="W106" s="25"/>
     </row>
-    <row r="107" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
         <v>30</v>
       </c>
@@ -8235,7 +8233,7 @@
       </c>
       <c r="W107" s="25"/>
     </row>
-    <row r="108" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A108" s="6" t="s">
         <v>30</v>
       </c>
@@ -8286,7 +8284,7 @@
       </c>
       <c r="W108" s="25"/>
     </row>
-    <row r="109" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A109" s="6" t="s">
         <v>30</v>
       </c>
@@ -8337,7 +8335,7 @@
       </c>
       <c r="W109" s="25"/>
     </row>
-    <row r="110" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
         <v>30</v>
       </c>
@@ -8388,7 +8386,7 @@
       </c>
       <c r="W110" s="25"/>
     </row>
-    <row r="111" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A111" s="6" t="s">
         <v>30</v>
       </c>
@@ -8439,7 +8437,7 @@
       </c>
       <c r="W111" s="25"/>
     </row>
-    <row r="112" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
         <v>30</v>
       </c>
@@ -8490,7 +8488,7 @@
       </c>
       <c r="W112" s="25"/>
     </row>
-    <row r="113" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
         <v>30</v>
       </c>
@@ -8541,7 +8539,7 @@
       </c>
       <c r="W113" s="25"/>
     </row>
-    <row r="114" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A114" s="6" t="s">
         <v>30</v>
       </c>
@@ -8592,7 +8590,7 @@
       </c>
       <c r="W114" s="25"/>
     </row>
-    <row r="115" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A115" s="6" t="s">
         <v>30</v>
       </c>
@@ -8641,7 +8639,7 @@
       </c>
       <c r="W115" s="25"/>
     </row>
-    <row r="116" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A116" s="6" t="s">
         <v>30</v>
       </c>
@@ -8690,7 +8688,7 @@
       </c>
       <c r="W116" s="25"/>
     </row>
-    <row r="117" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A117" s="6" t="s">
         <v>30</v>
       </c>
@@ -8739,7 +8737,7 @@
       </c>
       <c r="W117" s="25"/>
     </row>
-    <row r="118" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A118" s="6" t="s">
         <v>30</v>
       </c>
@@ -8788,7 +8786,7 @@
       </c>
       <c r="W118" s="25"/>
     </row>
-    <row r="119" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A119" s="6" t="s">
         <v>30</v>
       </c>
@@ -8837,7 +8835,7 @@
       </c>
       <c r="W119" s="25"/>
     </row>
-    <row r="120" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A120" s="6" t="s">
         <v>30</v>
       </c>
@@ -8886,7 +8884,7 @@
       </c>
       <c r="W120" s="25"/>
     </row>
-    <row r="121" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A121" s="6" t="s">
         <v>30</v>
       </c>
@@ -8935,7 +8933,7 @@
       </c>
       <c r="W121" s="25"/>
     </row>
-    <row r="122" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A122" s="6" t="s">
         <v>30</v>
       </c>
@@ -8984,7 +8982,7 @@
       </c>
       <c r="W122" s="25"/>
     </row>
-    <row r="123" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A123" s="6" t="s">
         <v>30</v>
       </c>
@@ -9033,7 +9031,7 @@
       </c>
       <c r="W123" s="25"/>
     </row>
-    <row r="124" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A124" s="6" t="s">
         <v>30</v>
       </c>
@@ -9082,7 +9080,7 @@
       </c>
       <c r="W124" s="25"/>
     </row>
-    <row r="125" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A125" s="6" t="s">
         <v>30</v>
       </c>
@@ -9131,7 +9129,7 @@
       </c>
       <c r="W125" s="25"/>
     </row>
-    <row r="126" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
         <v>30</v>
       </c>
@@ -9180,7 +9178,7 @@
       </c>
       <c r="W126" s="25"/>
     </row>
-    <row r="127" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
         <v>30</v>
       </c>
@@ -9229,7 +9227,7 @@
       </c>
       <c r="W127" s="25"/>
     </row>
-    <row r="128" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
         <v>30</v>
       </c>
@@ -9278,7 +9276,7 @@
       </c>
       <c r="W128" s="25"/>
     </row>
-    <row r="129" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
         <v>30</v>
       </c>
@@ -9329,7 +9327,7 @@
       </c>
       <c r="W129" s="25"/>
     </row>
-    <row r="130" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
         <v>30</v>
       </c>
@@ -9380,7 +9378,7 @@
       </c>
       <c r="W130" s="25"/>
     </row>
-    <row r="131" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
         <v>30</v>
       </c>
@@ -9431,7 +9429,7 @@
       </c>
       <c r="W131" s="25"/>
     </row>
-    <row r="132" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A132" s="6" t="s">
         <v>30</v>
       </c>
@@ -9480,7 +9478,7 @@
       </c>
       <c r="W132" s="25"/>
     </row>
-    <row r="133" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A133" s="6" t="s">
         <v>30</v>
       </c>
@@ -9529,7 +9527,7 @@
       </c>
       <c r="W133" s="25"/>
     </row>
-    <row r="134" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A134" s="6" t="s">
         <v>30</v>
       </c>
@@ -9578,7 +9576,7 @@
       </c>
       <c r="W134" s="25"/>
     </row>
-    <row r="135" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
         <v>30</v>
       </c>
@@ -9627,7 +9625,7 @@
       </c>
       <c r="W135" s="25"/>
     </row>
-    <row r="136" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A136" s="6" t="s">
         <v>30</v>
       </c>
@@ -9676,7 +9674,7 @@
       </c>
       <c r="W136" s="25"/>
     </row>
-    <row r="137" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A137" s="6" t="s">
         <v>30</v>
       </c>
@@ -9725,7 +9723,7 @@
       </c>
       <c r="W137" s="25"/>
     </row>
-    <row r="138" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A138" s="6" t="s">
         <v>30</v>
       </c>
@@ -9774,7 +9772,7 @@
       </c>
       <c r="W138" s="25"/>
     </row>
-    <row r="139" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A139" s="6" t="s">
         <v>30</v>
       </c>
@@ -9823,7 +9821,7 @@
       </c>
       <c r="W139" s="25"/>
     </row>
-    <row r="140" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A140" s="6" t="s">
         <v>30</v>
       </c>
@@ -9872,7 +9870,7 @@
       </c>
       <c r="W140" s="25"/>
     </row>
-    <row r="141" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
         <v>30</v>
       </c>
@@ -9921,7 +9919,7 @@
       </c>
       <c r="W141" s="25"/>
     </row>
-    <row r="142" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A142" s="6" t="s">
         <v>30</v>
       </c>
@@ -9970,7 +9968,7 @@
       </c>
       <c r="W142" s="25"/>
     </row>
-    <row r="143" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A143" s="6" t="s">
         <v>30</v>
       </c>
@@ -10021,7 +10019,7 @@
       </c>
       <c r="W143" s="25"/>
     </row>
-    <row r="144" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A144" s="6" t="s">
         <v>30</v>
       </c>
@@ -10072,7 +10070,7 @@
       </c>
       <c r="W144" s="25"/>
     </row>
-    <row r="145" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A145" s="6" t="s">
         <v>30</v>
       </c>
@@ -10121,7 +10119,7 @@
       </c>
       <c r="W145" s="25"/>
     </row>
-    <row r="146" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A146" s="6" t="s">
         <v>30</v>
       </c>
@@ -10170,7 +10168,7 @@
       </c>
       <c r="W146" s="25"/>
     </row>
-    <row r="147" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A147" s="6" t="s">
         <v>30</v>
       </c>
@@ -10219,7 +10217,7 @@
       </c>
       <c r="W147" s="25"/>
     </row>
-    <row r="148" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A148" s="6" t="s">
         <v>30</v>
       </c>
@@ -10268,7 +10266,7 @@
       </c>
       <c r="W148" s="25"/>
     </row>
-    <row r="149" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A149" s="6" t="s">
         <v>30</v>
       </c>
@@ -10317,7 +10315,7 @@
       </c>
       <c r="W149" s="25"/>
     </row>
-    <row r="150" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A150" s="6" t="s">
         <v>30</v>
       </c>
@@ -10366,7 +10364,7 @@
       </c>
       <c r="W150" s="25"/>
     </row>
-    <row r="151" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A151" s="6" t="s">
         <v>30</v>
       </c>
@@ -10415,7 +10413,7 @@
       </c>
       <c r="W151" s="25"/>
     </row>
-    <row r="152" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A152" s="6" t="s">
         <v>30</v>
       </c>
@@ -10466,7 +10464,7 @@
       </c>
       <c r="W152" s="25"/>
     </row>
-    <row r="153" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A153" s="6" t="s">
         <v>30</v>
       </c>
@@ -10515,7 +10513,7 @@
       </c>
       <c r="W153" s="25"/>
     </row>
-    <row r="154" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A154" s="6" t="s">
         <v>30</v>
       </c>
@@ -10564,7 +10562,7 @@
       </c>
       <c r="W154" s="25"/>
     </row>
-    <row r="155" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A155" s="6" t="s">
         <v>30</v>
       </c>
@@ -10613,7 +10611,7 @@
       </c>
       <c r="W155" s="25"/>
     </row>
-    <row r="156" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A156" s="6" t="s">
         <v>30</v>
       </c>
@@ -10662,7 +10660,7 @@
       </c>
       <c r="W156" s="25"/>
     </row>
-    <row r="157" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A157" s="6" t="s">
         <v>30</v>
       </c>
@@ -10711,7 +10709,7 @@
       </c>
       <c r="W157" s="25"/>
     </row>
-    <row r="158" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A158" s="6" t="s">
         <v>30</v>
       </c>
@@ -10762,7 +10760,7 @@
       </c>
       <c r="W158" s="25"/>
     </row>
-    <row r="159" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A159" s="6" t="s">
         <v>30</v>
       </c>
@@ -10813,7 +10811,7 @@
       </c>
       <c r="W159" s="25"/>
     </row>
-    <row r="160" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A160" s="6" t="s">
         <v>30</v>
       </c>
@@ -10864,7 +10862,7 @@
       </c>
       <c r="W160" s="25"/>
     </row>
-    <row r="161" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A161" s="6" t="s">
         <v>30</v>
       </c>
@@ -10915,7 +10913,7 @@
       </c>
       <c r="W161" s="25"/>
     </row>
-    <row r="162" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A162" s="6" t="s">
         <v>30</v>
       </c>
@@ -10966,7 +10964,7 @@
       </c>
       <c r="W162" s="25"/>
     </row>
-    <row r="163" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A163" s="6" t="s">
         <v>30</v>
       </c>
@@ -11017,7 +11015,7 @@
       </c>
       <c r="W163" s="25"/>
     </row>
-    <row r="164" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A164" s="6" t="s">
         <v>30</v>
       </c>
@@ -11068,7 +11066,7 @@
       </c>
       <c r="W164" s="25"/>
     </row>
-    <row r="165" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A165" s="6" t="s">
         <v>30</v>
       </c>
@@ -11119,7 +11117,7 @@
       </c>
       <c r="W165" s="25"/>
     </row>
-    <row r="166" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A166" s="6" t="s">
         <v>30</v>
       </c>
@@ -11170,7 +11168,7 @@
       </c>
       <c r="W166" s="25"/>
     </row>
-    <row r="167" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A167" s="6" t="s">
         <v>30</v>
       </c>
@@ -11221,7 +11219,7 @@
       </c>
       <c r="W167" s="25"/>
     </row>
-    <row r="168" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A168" s="6" t="s">
         <v>30</v>
       </c>
@@ -11270,7 +11268,7 @@
       </c>
       <c r="W168" s="25"/>
     </row>
-    <row r="169" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A169" s="6" t="s">
         <v>30</v>
       </c>
@@ -11319,7 +11317,7 @@
       </c>
       <c r="W169" s="25"/>
     </row>
-    <row r="170" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A170" s="6" t="s">
         <v>30</v>
       </c>
@@ -11368,7 +11366,7 @@
       </c>
       <c r="W170" s="25"/>
     </row>
-    <row r="171" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A171" s="6" t="s">
         <v>30</v>
       </c>
@@ -11417,7 +11415,7 @@
       </c>
       <c r="W171" s="25"/>
     </row>
-    <row r="172" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A172" s="6" t="s">
         <v>30</v>
       </c>
@@ -11466,7 +11464,7 @@
       </c>
       <c r="W172" s="25"/>
     </row>
-    <row r="173" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A173" s="6" t="s">
         <v>30</v>
       </c>
@@ -11515,7 +11513,7 @@
       </c>
       <c r="W173" s="25"/>
     </row>
-    <row r="174" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A174" s="6" t="s">
         <v>30</v>
       </c>
@@ -11564,7 +11562,7 @@
       </c>
       <c r="W174" s="25"/>
     </row>
-    <row r="175" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A175" s="6" t="s">
         <v>30</v>
       </c>
@@ -11613,7 +11611,7 @@
       </c>
       <c r="W175" s="25"/>
     </row>
-    <row r="176" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A176" s="6" t="s">
         <v>30</v>
       </c>
@@ -11664,7 +11662,7 @@
       </c>
       <c r="W176" s="25"/>
     </row>
-    <row r="177" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A177" s="6" t="s">
         <v>30</v>
       </c>
@@ -11713,7 +11711,7 @@
       </c>
       <c r="W177" s="25"/>
     </row>
-    <row r="178" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A178" s="6" t="s">
         <v>30</v>
       </c>
@@ -11762,7 +11760,7 @@
       </c>
       <c r="W178" s="25"/>
     </row>
-    <row r="179" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A179" s="6" t="s">
         <v>31</v>
       </c>
@@ -11811,7 +11809,7 @@
       </c>
       <c r="W179" s="25"/>
     </row>
-    <row r="180" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A180" s="6" t="s">
         <v>31</v>
       </c>
@@ -11860,7 +11858,7 @@
       </c>
       <c r="W180" s="25"/>
     </row>
-    <row r="181" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A181" s="6" t="s">
         <v>31</v>
       </c>
@@ -11909,7 +11907,7 @@
       </c>
       <c r="W181" s="25"/>
     </row>
-    <row r="182" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A182" s="6" t="s">
         <v>31</v>
       </c>
@@ -11958,7 +11956,7 @@
       </c>
       <c r="W182" s="25"/>
     </row>
-    <row r="183" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A183" s="6" t="s">
         <v>31</v>
       </c>
@@ -12009,7 +12007,7 @@
       </c>
       <c r="W183" s="25"/>
     </row>
-    <row r="184" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A184" s="6" t="s">
         <v>31</v>
       </c>
@@ -12058,7 +12056,7 @@
       </c>
       <c r="W184" s="25"/>
     </row>
-    <row r="185" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A185" s="6" t="s">
         <v>31</v>
       </c>
@@ -12107,7 +12105,7 @@
       </c>
       <c r="W185" s="25"/>
     </row>
-    <row r="186" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A186" s="6" t="s">
         <v>31</v>
       </c>
@@ -12156,7 +12154,7 @@
       </c>
       <c r="W186" s="25"/>
     </row>
-    <row r="187" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A187" s="6" t="s">
         <v>31</v>
       </c>
@@ -12221,7 +12219,7 @@
       </c>
       <c r="W187" s="25"/>
     </row>
-    <row r="188" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A188" s="6" t="s">
         <v>31</v>
       </c>
@@ -12270,7 +12268,7 @@
       </c>
       <c r="W188" s="25"/>
     </row>
-    <row r="189" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A189" s="6" t="s">
         <v>31</v>
       </c>
@@ -12319,7 +12317,7 @@
       </c>
       <c r="W189" s="25"/>
     </row>
-    <row r="190" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A190" s="6" t="s">
         <v>31</v>
       </c>
@@ -12368,7 +12366,7 @@
       </c>
       <c r="W190" s="25"/>
     </row>
-    <row r="191" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A191" s="6" t="s">
         <v>31</v>
       </c>
@@ -12417,7 +12415,7 @@
       </c>
       <c r="W191" s="25"/>
     </row>
-    <row r="192" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A192" s="6" t="s">
         <v>31</v>
       </c>
@@ -12466,7 +12464,7 @@
       </c>
       <c r="W192" s="25"/>
     </row>
-    <row r="193" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A193" s="6" t="s">
         <v>31</v>
       </c>
@@ -12515,7 +12513,7 @@
       </c>
       <c r="W193" s="25"/>
     </row>
-    <row r="194" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A194" s="6" t="s">
         <v>31</v>
       </c>
@@ -12564,7 +12562,7 @@
       </c>
       <c r="W194" s="25"/>
     </row>
-    <row r="195" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A195" s="6" t="s">
         <v>31</v>
       </c>
@@ -12613,7 +12611,7 @@
       </c>
       <c r="W195" s="25"/>
     </row>
-    <row r="196" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A196" s="6" t="s">
         <v>31</v>
       </c>
@@ -12662,7 +12660,7 @@
       </c>
       <c r="W196" s="25"/>
     </row>
-    <row r="197" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A197" s="6" t="s">
         <v>31</v>
       </c>
@@ -12711,7 +12709,7 @@
       </c>
       <c r="W197" s="25"/>
     </row>
-    <row r="198" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A198" s="6" t="s">
         <v>31</v>
       </c>
@@ -12760,7 +12758,7 @@
       </c>
       <c r="W198" s="25"/>
     </row>
-    <row r="199" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A199" s="6" t="s">
         <v>31</v>
       </c>
@@ -12809,7 +12807,7 @@
       </c>
       <c r="W199" s="25"/>
     </row>
-    <row r="200" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A200" s="6" t="s">
         <v>31</v>
       </c>
@@ -12858,7 +12856,7 @@
       </c>
       <c r="W200" s="25"/>
     </row>
-    <row r="201" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A201" s="6" t="s">
         <v>31</v>
       </c>
@@ -12907,7 +12905,7 @@
       </c>
       <c r="W201" s="25"/>
     </row>
-    <row r="202" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A202" s="6" t="s">
         <v>31</v>
       </c>
@@ -12956,7 +12954,7 @@
       </c>
       <c r="W202" s="25"/>
     </row>
-    <row r="203" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A203" s="6" t="s">
         <v>31</v>
       </c>
@@ -13005,7 +13003,7 @@
       </c>
       <c r="W203" s="25"/>
     </row>
-    <row r="204" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A204" s="6" t="s">
         <v>31</v>
       </c>
@@ -13054,7 +13052,7 @@
       </c>
       <c r="W204" s="25"/>
     </row>
-    <row r="205" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A205" s="6" t="s">
         <v>31</v>
       </c>
@@ -13103,7 +13101,7 @@
       </c>
       <c r="W205" s="25"/>
     </row>
-    <row r="206" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A206" s="6" t="s">
         <v>31</v>
       </c>
@@ -13201,7 +13199,7 @@
       </c>
       <c r="W207" s="25"/>
     </row>
-    <row r="208" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A208" s="6" t="s">
         <v>31</v>
       </c>
@@ -13250,7 +13248,7 @@
       </c>
       <c r="W208" s="25"/>
     </row>
-    <row r="209" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A209" s="6" t="s">
         <v>31</v>
       </c>
@@ -13299,7 +13297,7 @@
       </c>
       <c r="W209" s="25"/>
     </row>
-    <row r="210" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A210" s="6" t="s">
         <v>31</v>
       </c>
@@ -13348,7 +13346,7 @@
       </c>
       <c r="W210" s="25"/>
     </row>
-    <row r="211" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A211" s="6" t="s">
         <v>31</v>
       </c>
@@ -13397,7 +13395,7 @@
       </c>
       <c r="W211" s="25"/>
     </row>
-    <row r="212" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A212" s="19" t="s">
         <v>26</v>
       </c>
@@ -13446,7 +13444,7 @@
       </c>
       <c r="W212" s="25"/>
     </row>
-    <row r="213" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A213" s="6" t="s">
         <v>26</v>
       </c>
@@ -13503,7 +13501,7 @@
       </c>
       <c r="W213" s="25"/>
     </row>
-    <row r="214" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A214" s="6" t="s">
         <v>26</v>
       </c>
@@ -13560,7 +13558,7 @@
       </c>
       <c r="W214" s="25"/>
     </row>
-    <row r="215" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A215" s="6" t="s">
         <v>26</v>
       </c>
@@ -13609,7 +13607,7 @@
       </c>
       <c r="W215" s="25"/>
     </row>
-    <row r="216" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A216" s="6" t="s">
         <v>26</v>
       </c>
@@ -13658,7 +13656,7 @@
       </c>
       <c r="W216" s="25"/>
     </row>
-    <row r="217" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A217" s="6" t="s">
         <v>26</v>
       </c>
@@ -13707,7 +13705,7 @@
       </c>
       <c r="W217" s="25"/>
     </row>
-    <row r="218" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A218" s="6" t="s">
         <v>26</v>
       </c>
@@ -13756,7 +13754,7 @@
       </c>
       <c r="W218" s="25"/>
     </row>
-    <row r="219" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A219" s="6" t="s">
         <v>26</v>
       </c>
@@ -13805,7 +13803,7 @@
       </c>
       <c r="W219" s="25"/>
     </row>
-    <row r="220" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A220" s="6" t="s">
         <v>26</v>
       </c>
@@ -13854,7 +13852,7 @@
       </c>
       <c r="W220" s="25"/>
     </row>
-    <row r="221" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A221" s="6" t="s">
         <v>26</v>
       </c>
@@ -13903,7 +13901,7 @@
       </c>
       <c r="W221" s="25"/>
     </row>
-    <row r="222" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A222" s="6" t="s">
         <v>26</v>
       </c>
@@ -13952,7 +13950,7 @@
       </c>
       <c r="W222" s="25"/>
     </row>
-    <row r="223" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A223" s="6" t="s">
         <v>26</v>
       </c>
@@ -14001,7 +13999,7 @@
       </c>
       <c r="W223" s="25"/>
     </row>
-    <row r="224" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A224" s="6" t="s">
         <v>41</v>
       </c>
@@ -14052,7 +14050,7 @@
       </c>
       <c r="W224" s="25"/>
     </row>
-    <row r="225" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A225" s="6" t="s">
         <v>41</v>
       </c>
@@ -14109,7 +14107,7 @@
       </c>
       <c r="W225" s="25"/>
     </row>
-    <row r="226" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A226" s="6" t="s">
         <v>41</v>
       </c>
@@ -14158,7 +14156,7 @@
       </c>
       <c r="W226" s="25"/>
     </row>
-    <row r="227" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A227" s="6" t="s">
         <v>41</v>
       </c>
@@ -14207,7 +14205,7 @@
       </c>
       <c r="W227" s="25"/>
     </row>
-    <row r="228" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A228" s="6" t="s">
         <v>41</v>
       </c>
@@ -14256,7 +14254,7 @@
       </c>
       <c r="W228" s="25"/>
     </row>
-    <row r="229" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A229" s="6" t="s">
         <v>41</v>
       </c>
@@ -14305,7 +14303,7 @@
       </c>
       <c r="W229" s="25"/>
     </row>
-    <row r="230" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A230" s="6" t="s">
         <v>41</v>
       </c>
@@ -14354,7 +14352,7 @@
       </c>
       <c r="W230" s="25"/>
     </row>
-    <row r="231" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A231" s="6" t="s">
         <v>41</v>
       </c>
@@ -14403,7 +14401,7 @@
       </c>
       <c r="W231" s="25"/>
     </row>
-    <row r="232" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A232" s="6" t="s">
         <v>41</v>
       </c>
@@ -14452,7 +14450,7 @@
       </c>
       <c r="W232" s="25"/>
     </row>
-    <row r="233" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A233" s="6" t="s">
         <v>41</v>
       </c>
@@ -14501,7 +14499,7 @@
       </c>
       <c r="W233" s="25"/>
     </row>
-    <row r="234" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A234" s="6" t="s">
         <v>41</v>
       </c>
@@ -14550,7 +14548,7 @@
       </c>
       <c r="W234" s="25"/>
     </row>
-    <row r="235" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A235" s="6" t="s">
         <v>41</v>
       </c>
@@ -14599,7 +14597,7 @@
       </c>
       <c r="W235" s="25"/>
     </row>
-    <row r="236" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A236" s="6" t="s">
         <v>41</v>
       </c>
@@ -14648,7 +14646,7 @@
       </c>
       <c r="W236" s="25"/>
     </row>
-    <row r="237" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A237" s="6" t="s">
         <v>41</v>
       </c>
@@ -14697,7 +14695,7 @@
       </c>
       <c r="W237" s="25"/>
     </row>
-    <row r="238" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A238" s="6" t="s">
         <v>41</v>
       </c>
@@ -14746,7 +14744,7 @@
       </c>
       <c r="W238" s="25"/>
     </row>
-    <row r="239" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A239" s="6" t="s">
         <v>41</v>
       </c>
@@ -14795,7 +14793,7 @@
       </c>
       <c r="W239" s="25"/>
     </row>
-    <row r="240" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A240" s="6" t="s">
         <v>41</v>
       </c>
@@ -14844,7 +14842,7 @@
       </c>
       <c r="W240" s="25"/>
     </row>
-    <row r="241" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A241" s="6" t="s">
         <v>41</v>
       </c>
@@ -14893,7 +14891,7 @@
       </c>
       <c r="W241" s="25"/>
     </row>
-    <row r="242" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A242" s="6" t="s">
         <v>41</v>
       </c>
@@ -14942,7 +14940,7 @@
       </c>
       <c r="W242" s="25"/>
     </row>
-    <row r="243" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A243" s="6" t="s">
         <v>41</v>
       </c>
@@ -14991,7 +14989,7 @@
       </c>
       <c r="W243" s="25"/>
     </row>
-    <row r="244" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A244" s="6" t="s">
         <v>41</v>
       </c>
@@ -15040,7 +15038,7 @@
       </c>
       <c r="W244" s="25"/>
     </row>
-    <row r="245" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A245" s="6" t="s">
         <v>41</v>
       </c>
@@ -15089,7 +15087,7 @@
       </c>
       <c r="W245" s="25"/>
     </row>
-    <row r="246" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A246" s="6" t="s">
         <v>41</v>
       </c>
@@ -15138,7 +15136,7 @@
       </c>
       <c r="W246" s="25"/>
     </row>
-    <row r="247" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A247" s="6" t="s">
         <v>41</v>
       </c>
@@ -15187,7 +15185,7 @@
       </c>
       <c r="W247" s="25"/>
     </row>
-    <row r="248" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A248" s="6" t="s">
         <v>41</v>
       </c>
@@ -15236,7 +15234,7 @@
       </c>
       <c r="W248" s="25"/>
     </row>
-    <row r="249" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A249" s="6" t="s">
         <v>41</v>
       </c>
@@ -15285,7 +15283,7 @@
       </c>
       <c r="W249" s="25"/>
     </row>
-    <row r="250" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A250" s="6" t="s">
         <v>41</v>
       </c>
@@ -15334,7 +15332,7 @@
       </c>
       <c r="W250" s="25"/>
     </row>
-    <row r="251" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A251" s="6" t="s">
         <v>41</v>
       </c>
@@ -15383,7 +15381,7 @@
       </c>
       <c r="W251" s="25"/>
     </row>
-    <row r="252" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A252" s="6" t="s">
         <v>41</v>
       </c>
@@ -15432,7 +15430,7 @@
       </c>
       <c r="W252" s="25"/>
     </row>
-    <row r="253" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A253" s="6" t="s">
         <v>41</v>
       </c>
@@ -15481,7 +15479,7 @@
       </c>
       <c r="W253" s="25"/>
     </row>
-    <row r="254" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A254" s="6" t="s">
         <v>41</v>
       </c>
@@ -15530,7 +15528,7 @@
       </c>
       <c r="W254" s="25"/>
     </row>
-    <row r="255" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A255" s="6" t="s">
         <v>41</v>
       </c>
@@ -15579,7 +15577,7 @@
       </c>
       <c r="W255" s="25"/>
     </row>
-    <row r="256" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A256" s="6" t="s">
         <v>41</v>
       </c>
@@ -15628,7 +15626,7 @@
       </c>
       <c r="W256" s="25"/>
     </row>
-    <row r="257" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A257" s="6" t="s">
         <v>28</v>
       </c>
@@ -15689,7 +15687,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="258" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A258" s="6" t="s">
         <v>28</v>
       </c>
@@ -15750,7 +15748,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="259" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A259" s="6" t="s">
         <v>28</v>
       </c>
@@ -15803,7 +15801,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="260" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A260" s="6" t="s">
         <v>28</v>
       </c>
@@ -15856,7 +15854,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="261" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A261" s="6" t="s">
         <v>28</v>
       </c>
@@ -15909,7 +15907,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="262" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A262" s="6" t="s">
         <v>28</v>
       </c>
@@ -15962,7 +15960,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="263" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A263" s="6" t="s">
         <v>28</v>
       </c>
@@ -16015,7 +16013,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A264" s="6" t="s">
         <v>28</v>
       </c>
@@ -16068,7 +16066,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="265" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A265" s="6" t="s">
         <v>28</v>
       </c>
@@ -16121,7 +16119,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="266" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A266" s="6" t="s">
         <v>28</v>
       </c>
@@ -16174,7 +16172,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="267" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A267" s="6" t="s">
         <v>28</v>
       </c>
@@ -16227,7 +16225,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="268" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A268" s="6" t="s">
         <v>28</v>
       </c>
@@ -16280,7 +16278,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="269" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A269" s="6" t="s">
         <v>28</v>
       </c>
@@ -16333,7 +16331,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="270" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A270" s="6" t="s">
         <v>28</v>
       </c>
@@ -16386,7 +16384,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="271" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A271" s="6" t="s">
         <v>28</v>
       </c>
@@ -16441,7 +16439,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="272" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A272" s="6" t="s">
         <v>28</v>
       </c>
@@ -16494,7 +16492,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="273" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A273" s="6" t="s">
         <v>28</v>
       </c>
@@ -16547,7 +16545,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="274" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A274" s="6" t="s">
         <v>28</v>
       </c>
@@ -16600,7 +16598,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="275" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A275" s="6" t="s">
         <v>28</v>
       </c>
@@ -16653,7 +16651,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="276" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A276" s="6" t="s">
         <v>28</v>
       </c>
@@ -16706,7 +16704,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="277" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A277" s="6" t="s">
         <v>28</v>
       </c>
@@ -16759,7 +16757,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="278" spans="1:23" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:23" ht="112" x14ac:dyDescent="0.2">
       <c r="A278" s="6" t="s">
         <v>28</v>
       </c>
@@ -16812,7 +16810,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="279" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A279" s="6" t="s">
         <v>27</v>
       </c>
@@ -16873,7 +16871,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="280" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A280" s="6" t="s">
         <v>27</v>
       </c>
@@ -16926,7 +16924,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="281" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A281" s="6" t="s">
         <v>27</v>
       </c>
@@ -16979,7 +16977,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="282" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A282" s="6" t="s">
         <v>27</v>
       </c>
@@ -17032,7 +17030,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="283" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A283" s="6" t="s">
         <v>27</v>
       </c>
@@ -17085,7 +17083,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="284" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A284" s="6" t="s">
         <v>27</v>
       </c>
@@ -17138,7 +17136,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="285" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A285" s="6" t="s">
         <v>27</v>
       </c>
@@ -17191,7 +17189,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="286" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A286" s="6" t="s">
         <v>27</v>
       </c>
@@ -17244,7 +17242,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="287" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A287" s="6" t="s">
         <v>27</v>
       </c>
@@ -17297,7 +17295,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="288" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A288" s="6" t="s">
         <v>27</v>
       </c>
@@ -17350,7 +17348,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="289" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A289" s="6" t="s">
         <v>27</v>
       </c>
@@ -17403,7 +17401,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="290" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A290" s="6" t="s">
         <v>27</v>
       </c>
@@ -17456,7 +17454,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="291" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A291" s="6" t="s">
         <v>27</v>
       </c>
@@ -17509,7 +17507,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="292" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A292" s="6" t="s">
         <v>27</v>
       </c>
@@ -17562,7 +17560,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="293" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A293" s="6" t="s">
         <v>27</v>
       </c>
@@ -17615,7 +17613,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="294" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A294" s="6" t="s">
         <v>27</v>
       </c>
@@ -17668,7 +17666,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="295" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A295" s="6" t="s">
         <v>27</v>
       </c>
@@ -17721,7 +17719,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="296" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A296" s="6" t="s">
         <v>27</v>
       </c>
@@ -17774,7 +17772,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="297" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A297" s="6" t="s">
         <v>27</v>
       </c>
@@ -17827,7 +17825,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="298" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A298" s="6" t="s">
         <v>27</v>
       </c>
@@ -17880,7 +17878,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="299" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A299" s="6" t="s">
         <v>27</v>
       </c>
@@ -17933,7 +17931,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="300" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A300" s="6" t="s">
         <v>27</v>
       </c>
@@ -17986,7 +17984,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="301" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A301" s="6" t="s">
         <v>27</v>
       </c>
@@ -18039,7 +18037,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="302" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A302" s="6" t="s">
         <v>27</v>
       </c>
@@ -18092,7 +18090,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="303" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A303" s="6" t="s">
         <v>27</v>
       </c>
@@ -18145,7 +18143,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="304" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A304" s="6" t="s">
         <v>27</v>
       </c>
@@ -18198,7 +18196,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="305" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A305" s="6" t="s">
         <v>27</v>
       </c>
@@ -18251,7 +18249,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A306" s="6" t="s">
         <v>27</v>
       </c>
@@ -18304,7 +18302,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="307" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A307" s="6" t="s">
         <v>27</v>
       </c>
@@ -18357,7 +18355,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="308" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A308" s="6" t="s">
         <v>27</v>
       </c>
@@ -18410,7 +18408,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="309" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A309" s="6" t="s">
         <v>27</v>
       </c>
@@ -18463,7 +18461,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="310" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A310" s="6" t="s">
         <v>27</v>
       </c>
@@ -18516,7 +18514,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="311" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A311" s="6" t="s">
         <v>27</v>
       </c>
@@ -18569,7 +18567,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="312" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A312" s="6" t="s">
         <v>27</v>
       </c>
@@ -18622,7 +18620,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="313" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A313" s="6" t="s">
         <v>27</v>
       </c>
@@ -18675,7 +18673,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="314" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A314" s="6" t="s">
         <v>27</v>
       </c>
@@ -18728,7 +18726,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="315" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A315" s="6" t="s">
         <v>27</v>
       </c>
@@ -18781,7 +18779,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="316" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A316" s="6" t="s">
         <v>27</v>
       </c>
@@ -18834,7 +18832,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="317" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A317" s="6" t="s">
         <v>27</v>
       </c>
@@ -18887,7 +18885,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="318" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A318" s="6" t="s">
         <v>27</v>
       </c>
@@ -18940,7 +18938,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="319" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A319" s="6" t="s">
         <v>27</v>
       </c>
@@ -18993,7 +18991,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="320" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A320" s="6" t="s">
         <v>27</v>
       </c>
@@ -19046,7 +19044,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="321" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A321" s="6" t="s">
         <v>27</v>
       </c>
@@ -19099,7 +19097,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="322" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A322" s="6" t="s">
         <v>27</v>
       </c>
@@ -19154,7 +19152,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="323" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A323" s="6" t="s">
         <v>27</v>
       </c>
@@ -19209,7 +19207,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="324" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A324" s="6" t="s">
         <v>27</v>
       </c>
@@ -19262,7 +19260,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="325" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A325" s="6" t="s">
         <v>27</v>
       </c>
@@ -19315,7 +19313,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="326" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A326" s="6" t="s">
         <v>27</v>
       </c>
@@ -19368,7 +19366,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="327" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A327" s="6" t="s">
         <v>27</v>
       </c>
@@ -19421,7 +19419,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="328" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A328" s="6" t="s">
         <v>27</v>
       </c>
@@ -19474,7 +19472,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="329" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A329" s="6" t="s">
         <v>27</v>
       </c>
@@ -19527,7 +19525,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="330" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A330" s="6" t="s">
         <v>27</v>
       </c>
@@ -19580,7 +19578,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="331" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A331" s="6" t="s">
         <v>27</v>
       </c>
@@ -19633,7 +19631,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="332" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A332" s="6" t="s">
         <v>27</v>
       </c>
@@ -19686,7 +19684,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="333" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A333" s="6" t="s">
         <v>27</v>
       </c>
@@ -19739,7 +19737,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="334" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A334" s="6" t="s">
         <v>27</v>
       </c>
@@ -19792,7 +19790,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="335" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A335" s="6" t="s">
         <v>27</v>
       </c>
@@ -19845,7 +19843,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="336" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A336" s="6" t="s">
         <v>27</v>
       </c>
@@ -19898,7 +19896,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A337" s="6" t="s">
         <v>27</v>
       </c>
@@ -19967,7 +19965,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A338" s="6" t="s">
         <v>27</v>
       </c>
@@ -20020,7 +20018,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="339" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A339" s="6" t="s">
         <v>27</v>
       </c>
@@ -20073,7 +20071,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="340" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A340" s="6" t="s">
         <v>27</v>
       </c>
@@ -20126,7 +20124,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="341" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A341" s="6" t="s">
         <v>27</v>
       </c>
@@ -20179,7 +20177,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="342" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A342" s="6" t="s">
         <v>27</v>
       </c>
@@ -20232,7 +20230,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="343" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A343" s="6" t="s">
         <v>27</v>
       </c>
@@ -20285,7 +20283,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="344" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A344" s="6" t="s">
         <v>27</v>
       </c>
@@ -20338,7 +20336,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="345" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A345" s="6" t="s">
         <v>27</v>
       </c>
@@ -20391,7 +20389,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="346" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A346" s="6" t="s">
         <v>27</v>
       </c>
@@ -20444,7 +20442,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="347" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A347" s="6" t="s">
         <v>27</v>
       </c>
@@ -20497,7 +20495,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="348" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A348" s="6" t="s">
         <v>27</v>
       </c>
@@ -20550,7 +20548,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A349" s="6" t="s">
         <v>27</v>
       </c>
@@ -20603,7 +20601,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="350" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A350" s="6" t="s">
         <v>27</v>
       </c>
@@ -20656,7 +20654,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A351" s="6" t="s">
         <v>27</v>
       </c>
@@ -20709,7 +20707,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A352" s="6" t="s">
         <v>27</v>
       </c>
@@ -20762,7 +20760,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="353" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A353" s="6" t="s">
         <v>27</v>
       </c>
@@ -20815,7 +20813,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="354" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A354" s="6" t="s">
         <v>27</v>
       </c>
@@ -21017,7 +21015,7 @@
       </c>
       <c r="W357" s="25"/>
     </row>
-    <row r="358" spans="1:23" ht="64" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:23" ht="64" x14ac:dyDescent="0.2">
       <c r="A358" s="6" t="s">
         <v>43</v>
       </c>
@@ -21070,7 +21068,7 @@
       </c>
       <c r="W358" s="25"/>
     </row>
-    <row r="359" spans="1:23" ht="64" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:23" ht="64" x14ac:dyDescent="0.2">
       <c r="A359" s="6" t="s">
         <v>43</v>
       </c>
@@ -21121,7 +21119,7 @@
       </c>
       <c r="W359" s="25"/>
     </row>
-    <row r="360" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="s">
         <v>13</v>
       </c>
@@ -21178,7 +21176,7 @@
       </c>
       <c r="W360" s="25"/>
     </row>
-    <row r="361" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A361" s="1" t="s">
         <v>13</v>
       </c>
@@ -21235,7 +21233,7 @@
       </c>
       <c r="W361" s="25"/>
     </row>
-    <row r="362" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="s">
         <v>13</v>
       </c>
@@ -21288,7 +21286,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="363" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="s">
         <v>13</v>
       </c>
@@ -21339,7 +21337,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="364" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A364" s="6" t="s">
         <v>50</v>
       </c>
@@ -21388,7 +21386,7 @@
       </c>
       <c r="W364" s="25"/>
     </row>
-    <row r="365" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A365" s="6" t="s">
         <v>50</v>
       </c>
@@ -21437,7 +21435,7 @@
       </c>
       <c r="W365" s="25"/>
     </row>
-    <row r="366" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A366" s="6" t="s">
         <v>50</v>
       </c>
@@ -21486,7 +21484,7 @@
       </c>
       <c r="W366" s="25"/>
     </row>
-    <row r="367" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A367" s="6" t="s">
         <v>50</v>
       </c>
@@ -21535,7 +21533,7 @@
       </c>
       <c r="W367" s="25"/>
     </row>
-    <row r="368" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A368" s="6" t="s">
         <v>50</v>
       </c>
@@ -21584,7 +21582,7 @@
       </c>
       <c r="W368" s="25"/>
     </row>
-    <row r="369" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A369" s="6" t="s">
         <v>50</v>
       </c>
@@ -21633,7 +21631,7 @@
       </c>
       <c r="W369" s="25"/>
     </row>
-    <row r="370" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A370" s="6" t="s">
         <v>50</v>
       </c>
@@ -21682,7 +21680,7 @@
       </c>
       <c r="W370" s="25"/>
     </row>
-    <row r="371" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A371" s="6" t="s">
         <v>50</v>
       </c>
@@ -21731,7 +21729,7 @@
       </c>
       <c r="W371" s="25"/>
     </row>
-    <row r="372" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A372" s="6" t="s">
         <v>50</v>
       </c>
@@ -21780,7 +21778,7 @@
       </c>
       <c r="W372" s="25"/>
     </row>
-    <row r="373" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A373" s="6" t="s">
         <v>50</v>
       </c>
@@ -21831,7 +21829,7 @@
       </c>
       <c r="W373" s="25"/>
     </row>
-    <row r="374" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A374" s="6" t="s">
         <v>50</v>
       </c>
@@ -21880,7 +21878,7 @@
       </c>
       <c r="W374" s="25"/>
     </row>
-    <row r="375" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A375" s="6" t="s">
         <v>50</v>
       </c>
@@ -21929,7 +21927,7 @@
       </c>
       <c r="W375" s="25"/>
     </row>
-    <row r="376" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A376" s="6" t="s">
         <v>50</v>
       </c>
@@ -21978,7 +21976,7 @@
       </c>
       <c r="W376" s="25"/>
     </row>
-    <row r="377" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A377" s="6" t="s">
         <v>50</v>
       </c>
@@ -22027,7 +22025,7 @@
       </c>
       <c r="W377" s="25"/>
     </row>
-    <row r="378" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A378" s="6" t="s">
         <v>50</v>
       </c>
@@ -22076,7 +22074,7 @@
       </c>
       <c r="W378" s="25"/>
     </row>
-    <row r="379" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A379" s="6" t="s">
         <v>50</v>
       </c>
@@ -22125,7 +22123,7 @@
       </c>
       <c r="W379" s="25"/>
     </row>
-    <row r="380" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A380" s="6" t="s">
         <v>50</v>
       </c>
@@ -22174,7 +22172,7 @@
       </c>
       <c r="W380" s="25"/>
     </row>
-    <row r="381" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A381" s="6" t="s">
         <v>50</v>
       </c>
@@ -22223,7 +22221,7 @@
       </c>
       <c r="W381" s="25"/>
     </row>
-    <row r="382" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A382" s="6" t="s">
         <v>50</v>
       </c>
@@ -22272,7 +22270,7 @@
       </c>
       <c r="W382" s="25"/>
     </row>
-    <row r="383" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A383" s="6" t="s">
         <v>50</v>
       </c>
@@ -22321,7 +22319,7 @@
       </c>
       <c r="W383" s="25"/>
     </row>
-    <row r="384" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A384" s="6" t="s">
         <v>50</v>
       </c>
@@ -22370,7 +22368,7 @@
       </c>
       <c r="W384" s="25"/>
     </row>
-    <row r="385" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A385" s="6" t="s">
         <v>50</v>
       </c>
@@ -22419,7 +22417,7 @@
       </c>
       <c r="W385" s="25"/>
     </row>
-    <row r="386" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A386" s="6" t="s">
         <v>50</v>
       </c>
@@ -22468,7 +22466,7 @@
       </c>
       <c r="W386" s="25"/>
     </row>
-    <row r="387" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A387" s="6" t="s">
         <v>50</v>
       </c>
@@ -22517,7 +22515,7 @@
       </c>
       <c r="W387" s="25"/>
     </row>
-    <row r="388" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A388" s="6" t="s">
         <v>50</v>
       </c>
@@ -22566,7 +22564,7 @@
       </c>
       <c r="W388" s="25"/>
     </row>
-    <row r="389" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A389" s="6" t="s">
         <v>50</v>
       </c>
@@ -22615,7 +22613,7 @@
       </c>
       <c r="W389" s="25"/>
     </row>
-    <row r="390" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A390" s="6" t="s">
         <v>50</v>
       </c>
@@ -22664,7 +22662,7 @@
       </c>
       <c r="W390" s="25"/>
     </row>
-    <row r="391" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A391" s="6" t="s">
         <v>50</v>
       </c>
@@ -22713,7 +22711,7 @@
       </c>
       <c r="W391" s="25"/>
     </row>
-    <row r="392" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A392" s="6" t="s">
         <v>50</v>
       </c>
@@ -22762,7 +22760,7 @@
       </c>
       <c r="W392" s="25"/>
     </row>
-    <row r="393" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A393" s="6" t="s">
         <v>50</v>
       </c>
@@ -22811,7 +22809,7 @@
       </c>
       <c r="W393" s="25"/>
     </row>
-    <row r="394" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A394" s="6" t="s">
         <v>50</v>
       </c>
@@ -22860,7 +22858,7 @@
       </c>
       <c r="W394" s="25"/>
     </row>
-    <row r="395" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A395" s="6" t="s">
         <v>338</v>
       </c>
@@ -22909,7 +22907,7 @@
       </c>
       <c r="W395" s="24"/>
     </row>
-    <row r="396" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A396" s="6" t="s">
         <v>338</v>
       </c>
@@ -22958,7 +22956,7 @@
       </c>
       <c r="W396" s="24"/>
     </row>
-    <row r="397" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A397" s="6" t="s">
         <v>338</v>
       </c>
@@ -23007,7 +23005,7 @@
       </c>
       <c r="W397" s="24"/>
     </row>
-    <row r="398" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A398" s="6" t="s">
         <v>338</v>
       </c>
@@ -23056,7 +23054,7 @@
       </c>
       <c r="W398" s="24"/>
     </row>
-    <row r="399" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A399" s="6" t="s">
         <v>338</v>
       </c>
@@ -23105,7 +23103,7 @@
       </c>
       <c r="W399" s="24"/>
     </row>
-    <row r="400" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A400" s="6" t="s">
         <v>338</v>
       </c>
@@ -23154,7 +23152,7 @@
       </c>
       <c r="W400" s="24"/>
     </row>
-    <row r="401" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A401" s="6" t="s">
         <v>338</v>
       </c>
@@ -23203,7 +23201,7 @@
       </c>
       <c r="W401" s="24"/>
     </row>
-    <row r="402" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A402" s="6" t="s">
         <v>338</v>
       </c>
@@ -23252,7 +23250,7 @@
       </c>
       <c r="W402" s="24"/>
     </row>
-    <row r="403" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A403" s="6" t="s">
         <v>338</v>
       </c>
@@ -23301,7 +23299,7 @@
       </c>
       <c r="W403" s="24"/>
     </row>
-    <row r="404" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A404" s="6" t="s">
         <v>338</v>
       </c>
@@ -23350,7 +23348,7 @@
       </c>
       <c r="W404" s="24"/>
     </row>
-    <row r="405" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A405" s="6" t="s">
         <v>338</v>
       </c>
@@ -23399,7 +23397,7 @@
       </c>
       <c r="W405" s="24"/>
     </row>
-    <row r="406" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A406" s="6" t="s">
         <v>338</v>
       </c>
@@ -23448,7 +23446,7 @@
       </c>
       <c r="W406" s="24"/>
     </row>
-    <row r="407" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A407" s="6" t="s">
         <v>338</v>
       </c>
@@ -23497,7 +23495,7 @@
       </c>
       <c r="W407" s="24"/>
     </row>
-    <row r="408" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A408" s="6" t="s">
         <v>354</v>
       </c>
@@ -23546,7 +23544,7 @@
       </c>
       <c r="W408" s="24"/>
     </row>
-    <row r="409" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A409" s="6" t="s">
         <v>354</v>
       </c>
@@ -23595,7 +23593,7 @@
       </c>
       <c r="W409" s="24"/>
     </row>
-    <row r="410" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A410" s="6" t="s">
         <v>354</v>
       </c>
@@ -23644,7 +23642,7 @@
       </c>
       <c r="W410" s="24"/>
     </row>
-    <row r="411" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A411" s="6" t="s">
         <v>354</v>
       </c>
@@ -23693,7 +23691,7 @@
       </c>
       <c r="W411" s="24"/>
     </row>
-    <row r="412" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A412" s="6" t="s">
         <v>354</v>
       </c>
@@ -23742,7 +23740,7 @@
       </c>
       <c r="W412" s="24"/>
     </row>
-    <row r="413" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A413" s="6" t="s">
         <v>354</v>
       </c>
@@ -23791,7 +23789,7 @@
       </c>
       <c r="W413" s="24"/>
     </row>
-    <row r="414" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A414" s="6" t="s">
         <v>354</v>
       </c>
@@ -23840,7 +23838,7 @@
       </c>
       <c r="W414" s="24"/>
     </row>
-    <row r="415" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A415" s="6" t="s">
         <v>354</v>
       </c>
@@ -23889,7 +23887,7 @@
       </c>
       <c r="W415" s="24"/>
     </row>
-    <row r="416" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A416" s="6" t="s">
         <v>354</v>
       </c>
@@ -23938,7 +23936,7 @@
       </c>
       <c r="W416" s="24"/>
     </row>
-    <row r="417" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A417" s="6" t="s">
         <v>354</v>
       </c>
@@ -23987,7 +23985,7 @@
       </c>
       <c r="W417" s="24"/>
     </row>
-    <row r="418" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A418" s="6" t="s">
         <v>354</v>
       </c>
@@ -24036,7 +24034,7 @@
       </c>
       <c r="W418" s="24"/>
     </row>
-    <row r="419" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A419" s="6" t="s">
         <v>354</v>
       </c>
@@ -24085,7 +24083,7 @@
       </c>
       <c r="W419" s="24"/>
     </row>
-    <row r="420" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A420" s="6" t="s">
         <v>354</v>
       </c>
@@ -24134,7 +24132,7 @@
       </c>
       <c r="W420" s="24"/>
     </row>
-    <row r="421" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A421" s="6" t="s">
         <v>354</v>
       </c>
@@ -24183,7 +24181,7 @@
       </c>
       <c r="W421" s="24"/>
     </row>
-    <row r="422" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A422" s="6" t="s">
         <v>354</v>
       </c>
@@ -24232,7 +24230,7 @@
       </c>
       <c r="W422" s="24"/>
     </row>
-    <row r="423" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A423" s="6" t="s">
         <v>354</v>
       </c>
@@ -24281,7 +24279,7 @@
       </c>
       <c r="W423" s="24"/>
     </row>
-    <row r="424" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A424" s="6" t="s">
         <v>354</v>
       </c>
@@ -24330,7 +24328,7 @@
       </c>
       <c r="W424" s="24"/>
     </row>
-    <row r="425" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A425" s="6" t="s">
         <v>354</v>
       </c>
@@ -24379,7 +24377,7 @@
       </c>
       <c r="W425" s="24"/>
     </row>
-    <row r="426" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A426" s="6" t="s">
         <v>354</v>
       </c>
@@ -24428,7 +24426,7 @@
       </c>
       <c r="W426" s="24"/>
     </row>
-    <row r="427" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A427" s="6" t="s">
         <v>354</v>
       </c>
@@ -24477,7 +24475,7 @@
       </c>
       <c r="W427" s="24"/>
     </row>
-    <row r="428" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A428" s="6" t="s">
         <v>354</v>
       </c>
@@ -24526,7 +24524,7 @@
       </c>
       <c r="W428" s="24"/>
     </row>
-    <row r="429" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A429" s="6" t="s">
         <v>354</v>
       </c>
@@ -24575,7 +24573,7 @@
       </c>
       <c r="W429" s="24"/>
     </row>
-    <row r="430" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A430" s="6" t="s">
         <v>354</v>
       </c>
@@ -24624,7 +24622,7 @@
       </c>
       <c r="W430" s="24"/>
     </row>
-    <row r="431" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A431" s="6" t="s">
         <v>354</v>
       </c>
@@ -24673,7 +24671,7 @@
       </c>
       <c r="W431" s="24"/>
     </row>
-    <row r="432" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A432" s="6" t="s">
         <v>380</v>
       </c>
@@ -24724,7 +24722,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="433" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A433" s="6" t="s">
         <v>380</v>
       </c>
@@ -24775,7 +24773,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="434" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A434" s="6" t="s">
         <v>380</v>
       </c>
@@ -24826,7 +24824,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="435" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A435" s="6" t="s">
         <v>380</v>
       </c>
@@ -24877,7 +24875,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="436" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A436" s="6" t="s">
         <v>380</v>
       </c>
@@ -24928,7 +24926,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="437" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A437" s="6" t="s">
         <v>380</v>
       </c>
@@ -24979,7 +24977,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="438" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A438" s="6" t="s">
         <v>380</v>
       </c>
@@ -25030,7 +25028,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="439" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A439" s="6" t="s">
         <v>380</v>
       </c>
@@ -25081,7 +25079,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="440" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A440" s="6" t="s">
         <v>380</v>
       </c>
@@ -25132,7 +25130,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="441" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A441" s="6" t="s">
         <v>380</v>
       </c>
@@ -25183,7 +25181,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="442" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A442" s="6" t="s">
         <v>380</v>
       </c>
@@ -25234,7 +25232,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="443" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A443" s="6" t="s">
         <v>380</v>
       </c>
@@ -25285,7 +25283,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="444" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A444" s="6" t="s">
         <v>380</v>
       </c>
@@ -25336,7 +25334,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="445" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A445" s="6" t="s">
         <v>395</v>
       </c>
@@ -25387,7 +25385,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="446" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A446" s="6" t="s">
         <v>395</v>
       </c>
@@ -25438,7 +25436,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="447" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A447" s="6" t="s">
         <v>395</v>
       </c>
@@ -25489,7 +25487,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="448" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A448" s="6" t="s">
         <v>395</v>
       </c>
@@ -25540,7 +25538,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="449" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A449" s="6" t="s">
         <v>395</v>
       </c>
@@ -25591,7 +25589,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="450" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A450" s="6" t="s">
         <v>395</v>
       </c>
@@ -25642,7 +25640,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="451" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A451" s="6" t="s">
         <v>395</v>
       </c>
@@ -25693,7 +25691,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="452" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A452" s="6" t="s">
         <v>395</v>
       </c>
@@ -25744,7 +25742,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="453" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A453" s="6" t="s">
         <v>395</v>
       </c>
@@ -25795,7 +25793,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="454" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A454" s="6" t="s">
         <v>395</v>
       </c>
@@ -25846,7 +25844,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="455" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A455" s="6" t="s">
         <v>395</v>
       </c>
@@ -25897,7 +25895,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="456" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A456" s="6" t="s">
         <v>395</v>
       </c>
@@ -25948,7 +25946,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="457" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A457" s="6" t="s">
         <v>395</v>
       </c>
@@ -25999,7 +25997,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="458" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A458" s="6" t="s">
         <v>395</v>
       </c>
@@ -26050,7 +26048,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="459" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A459" s="6" t="s">
         <v>395</v>
       </c>
@@ -26101,7 +26099,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="460" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A460" s="6" t="s">
         <v>395</v>
       </c>
@@ -26152,7 +26150,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="461" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A461" s="6" t="s">
         <v>395</v>
       </c>
@@ -26203,7 +26201,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="462" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A462" s="6" t="s">
         <v>395</v>
       </c>
@@ -26254,7 +26252,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="463" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A463" s="6" t="s">
         <v>395</v>
       </c>
@@ -26305,7 +26303,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="464" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A464" s="6" t="s">
         <v>395</v>
       </c>
@@ -26356,7 +26354,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="465" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A465" s="6" t="s">
         <v>395</v>
       </c>
@@ -26407,7 +26405,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="466" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A466" s="6" t="s">
         <v>395</v>
       </c>
@@ -26458,7 +26456,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="467" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A467" s="6" t="s">
         <v>395</v>
       </c>
@@ -26509,7 +26507,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="468" spans="1:23" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A468" s="6" t="s">
         <v>395</v>
       </c>
@@ -26560,7 +26558,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="469" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A469" s="6" t="s">
         <v>421</v>
       </c>
@@ -26609,7 +26607,7 @@
       </c>
       <c r="W469" s="24"/>
     </row>
-    <row r="470" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A470" s="6" t="s">
         <v>421</v>
       </c>
@@ -26658,7 +26656,7 @@
       </c>
       <c r="W470" s="24"/>
     </row>
-    <row r="471" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A471" s="6" t="s">
         <v>421</v>
       </c>
@@ -26707,7 +26705,7 @@
       </c>
       <c r="W471" s="24"/>
     </row>
-    <row r="472" spans="1:23" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:23" ht="48" x14ac:dyDescent="0.2">
       <c r="A472" s="6" t="s">
         <v>421</v>
       </c>
@@ -26756,7 +26754,7 @@
       </c>
       <c r="W472" s="24"/>
     </row>
-    <row r="473" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A473" s="17" t="s">
         <v>427</v>
       </c>
@@ -26805,7 +26803,7 @@
       </c>
       <c r="W473" s="24"/>
     </row>
-    <row r="474" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A474" s="17" t="s">
         <v>427</v>
       </c>
@@ -26854,7 +26852,7 @@
       </c>
       <c r="W474" s="24"/>
     </row>
-    <row r="475" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A475" s="17" t="s">
         <v>427</v>
       </c>
@@ -26903,7 +26901,7 @@
       </c>
       <c r="W475" s="24"/>
     </row>
-    <row r="476" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A476" s="17" t="s">
         <v>427</v>
       </c>
@@ -26952,7 +26950,7 @@
       </c>
       <c r="W476" s="24"/>
     </row>
-    <row r="477" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A477" s="17" t="s">
         <v>427</v>
       </c>
@@ -27001,7 +26999,7 @@
       </c>
       <c r="W477" s="24"/>
     </row>
-    <row r="478" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A478" s="17" t="s">
         <v>427</v>
       </c>
@@ -27050,7 +27048,7 @@
       </c>
       <c r="W478" s="24"/>
     </row>
-    <row r="479" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A479" s="17" t="s">
         <v>427</v>
       </c>
@@ -27099,7 +27097,7 @@
       </c>
       <c r="W479" s="24"/>
     </row>
-    <row r="480" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A480" s="17" t="s">
         <v>427</v>
       </c>
@@ -27148,7 +27146,7 @@
       </c>
       <c r="W480" s="24"/>
     </row>
-    <row r="481" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A481" s="17" t="s">
         <v>427</v>
       </c>
@@ -27197,7 +27195,7 @@
       </c>
       <c r="W481" s="24"/>
     </row>
-    <row r="482" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A482" s="17" t="s">
         <v>427</v>
       </c>
@@ -27246,7 +27244,7 @@
       </c>
       <c r="W482" s="24"/>
     </row>
-    <row r="483" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A483" s="17" t="s">
         <v>427</v>
       </c>
@@ -27295,7 +27293,7 @@
       </c>
       <c r="W483" s="24"/>
     </row>
-    <row r="484" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A484" s="17" t="s">
         <v>427</v>
       </c>
@@ -27344,7 +27342,7 @@
       </c>
       <c r="W484" s="24"/>
     </row>
-    <row r="485" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A485" s="17" t="s">
         <v>427</v>
       </c>
@@ -27393,7 +27391,7 @@
       </c>
       <c r="W485" s="24"/>
     </row>
-    <row r="486" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A486" s="17" t="s">
         <v>427</v>
       </c>
@@ -27442,7 +27440,7 @@
       </c>
       <c r="W486" s="24"/>
     </row>
-    <row r="487" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A487" s="17" t="s">
         <v>427</v>
       </c>
@@ -27491,7 +27489,7 @@
       </c>
       <c r="W487" s="24"/>
     </row>
-    <row r="488" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A488" s="17" t="s">
         <v>427</v>
       </c>
@@ -27540,7 +27538,7 @@
       </c>
       <c r="W488" s="24"/>
     </row>
-    <row r="489" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A489" s="17" t="s">
         <v>428</v>
       </c>
@@ -27589,7 +27587,7 @@
       </c>
       <c r="W489" s="24"/>
     </row>
-    <row r="490" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A490" s="17" t="s">
         <v>428</v>
       </c>
@@ -27648,7 +27646,7 @@
       </c>
       <c r="W490" s="25"/>
     </row>
-    <row r="491" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A491" s="17" t="s">
         <v>428</v>
       </c>
@@ -27699,7 +27697,7 @@
       </c>
       <c r="W491" s="25"/>
     </row>
-    <row r="492" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A492" s="17" t="s">
         <v>428</v>
       </c>
@@ -27748,7 +27746,7 @@
       </c>
       <c r="W492" s="24"/>
     </row>
-    <row r="493" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A493" s="17" t="s">
         <v>428</v>
       </c>
@@ -27797,7 +27795,7 @@
       </c>
       <c r="W493" s="24"/>
     </row>
-    <row r="494" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A494" s="17" t="s">
         <v>428</v>
       </c>
@@ -27846,7 +27844,7 @@
       </c>
       <c r="W494" s="24"/>
     </row>
-    <row r="495" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A495" s="17" t="s">
         <v>428</v>
       </c>
@@ -27895,7 +27893,7 @@
       </c>
       <c r="W495" s="24"/>
     </row>
-    <row r="496" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A496" s="17" t="s">
         <v>428</v>
       </c>
@@ -27944,7 +27942,7 @@
       </c>
       <c r="W496" s="24"/>
     </row>
-    <row r="497" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A497" s="17" t="s">
         <v>428</v>
       </c>
@@ -27993,7 +27991,7 @@
       </c>
       <c r="W497" s="24"/>
     </row>
-    <row r="498" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A498" s="17" t="s">
         <v>428</v>
       </c>
@@ -28042,7 +28040,7 @@
       </c>
       <c r="W498" s="24"/>
     </row>
-    <row r="499" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A499" s="17" t="s">
         <v>428</v>
       </c>
@@ -28091,7 +28089,7 @@
       </c>
       <c r="W499" s="24"/>
     </row>
-    <row r="500" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A500" s="17" t="s">
         <v>428</v>
       </c>
@@ -28140,7 +28138,7 @@
       </c>
       <c r="W500" s="24"/>
     </row>
-    <row r="501" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A501" s="17" t="s">
         <v>428</v>
       </c>
@@ -28189,7 +28187,7 @@
       </c>
       <c r="W501" s="24"/>
     </row>
-    <row r="502" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A502" s="17" t="s">
         <v>428</v>
       </c>
@@ -28238,7 +28236,7 @@
       </c>
       <c r="W502" s="24"/>
     </row>
-    <row r="503" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A503" s="17" t="s">
         <v>428</v>
       </c>
@@ -28287,7 +28285,7 @@
       </c>
       <c r="W503" s="24"/>
     </row>
-    <row r="504" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A504" s="17" t="s">
         <v>428</v>
       </c>
@@ -28336,7 +28334,7 @@
       </c>
       <c r="W504" s="24"/>
     </row>
-    <row r="505" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A505" s="17" t="s">
         <v>428</v>
       </c>
@@ -28385,7 +28383,7 @@
       </c>
       <c r="W505" s="24"/>
     </row>
-    <row r="506" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A506" s="17" t="s">
         <v>428</v>
       </c>
@@ -28434,7 +28432,7 @@
       </c>
       <c r="W506" s="24"/>
     </row>
-    <row r="507" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A507" s="17" t="s">
         <v>428</v>
       </c>
@@ -28483,7 +28481,7 @@
       </c>
       <c r="W507" s="24"/>
     </row>
-    <row r="508" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A508" s="17" t="s">
         <v>428</v>
       </c>
@@ -28532,7 +28530,7 @@
       </c>
       <c r="W508" s="24"/>
     </row>
-    <row r="509" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A509" s="17" t="s">
         <v>428</v>
       </c>
@@ -28581,7 +28579,7 @@
       </c>
       <c r="W509" s="24"/>
     </row>
-    <row r="510" spans="1:23" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:23" ht="16" x14ac:dyDescent="0.2">
       <c r="A510" s="17" t="s">
         <v>428</v>
       </c>
@@ -28640,19 +28638,7 @@
       <c r="H513" s="23"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W510" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="era_vene_16_ 744_22"/>
-        <filter val="era_vene_7_ 95_1"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="21">
-      <filters>
-        <filter val="TRUE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:W510" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2:A13">
     <cfRule type="expression" dxfId="127" priority="80">
